--- a/docs/doc.xlsx
+++ b/docs/doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_projects\BA-style-homepage-backend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5F160BC-E554-4C42-B32D-892D93075D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75552B75-2B93-416F-9AA3-1F302A299C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="70">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -92,187 +92,207 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>yyyy-mm-dd格式字符串</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>varchar(15)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>お知らせテーブル</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ミッションテーブル</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tag_index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:イベント, 2:旅行, 3:開発</t>
+  </si>
+  <si>
+    <t>标签</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>times</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已完成次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>max_times</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标完成次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>complete_date</t>
+  </si>
+  <si>
+    <t>完成日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>详细信息链接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_percent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成进度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRANTED STORED： floor((`times` / `max_times`))</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置为xxx开头的字符串则会在点击时显示xxx后的文本信息提示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>パッチノートテーブル</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>title</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp_daily_visits</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visit_date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当日访问量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>datetime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ON UPDATE current_timestamp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>page</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visit_count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>varchar(100)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unique1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>访问日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>访问页面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>各页面的日访问量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>decimal(10, 2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>title_ja</t>
+  </si>
+  <si>
+    <t>contents_ja</t>
+  </si>
+  <si>
+    <t>hp_contents_announcement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp_contents_mission</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp_contents_patch_note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detail_url_ja</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detail_url_zh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detail_url_en</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>time</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>通知日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>varchar(15)</t>
   </si>
   <si>
     <t>yyyy-mm-dd格式字符串</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>varchar(15)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>お知らせテーブル</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ミッションテーブル</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tag_index</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:イベント, 2:旅行, 3:開発</t>
-  </si>
-  <si>
-    <t>标签</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>times</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已完成次数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>max_times</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标完成次数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>complete_date</t>
-  </si>
-  <si>
-    <t>完成日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>详细信息链接</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>_percent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>完成进度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GRANTED STORED： floor((`times` / `max_times`))</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设置为xxx开头的字符串则会在点击时显示xxx后的文本信息提示</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>パッチノートテーブル</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>title</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hp_daily_visits</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>visit_date</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当日访问量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update_time</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>datetime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>date</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ON UPDATE current_timestamp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>page</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>visit_count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>varchar(100)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>unique1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>访问日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>访问页面</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>各页面的日访问量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>decimal(10, 2)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>title_ja</t>
-  </si>
-  <si>
-    <t>contents_ja</t>
-  </si>
-  <si>
-    <t>hp_contents_announcement</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hp_contents_mission</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hp_contents_patch_note</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>detail_url_ja</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>detail_url_zh</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>detail_url_en</t>
+  </si>
+  <si>
+    <t>delete_flg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除标记</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>varchar(1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0: 正常，1: 已删除</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -816,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:E42"/>
+  <dimension ref="B1:E45"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.375" customWidth="1"/>
@@ -829,11 +849,11 @@
     <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
       <c r="B2" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -867,7 +887,7 @@
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
@@ -903,7 +923,7 @@
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>7</v>
@@ -937,91 +957,93 @@
       </c>
       <c r="E10" s="3"/>
     </row>
-    <row r="11" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="5" t="s">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B11" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B13" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="9"/>
-    </row>
-    <row r="14" spans="2:5" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="13" t="s">
+      <c r="E14" s="9"/>
+    </row>
+    <row r="15" spans="2:5" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C15" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D15" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E15" s="15" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B15" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E17" s="3"/>
+      <c r="E17" s="3" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>8</v>
@@ -1030,10 +1052,10 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>8</v>
@@ -1042,278 +1064,318 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="E20" s="3"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E21" s="3"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>19</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="E22" s="3"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B23" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>36</v>
+      <c r="B23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B24" s="10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B25" s="10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B26" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B27" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26" s="6" t="s">
+    </row>
+    <row r="28" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B30" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="27" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B28" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="9"/>
-    </row>
-    <row r="29" spans="2:5" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="13" t="s">
+      <c r="E30" s="9"/>
+    </row>
+    <row r="31" spans="2:5" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C31" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D31" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E31" s="15" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B30" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B31" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B34" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="3"/>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B35" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E33" s="3"/>
-    </row>
-    <row r="34" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="4" t="s">
+      <c r="E35" s="3"/>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B36" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C36" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D36" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E34" s="6"/>
-    </row>
-    <row r="35" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B36" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" s="9"/>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B37" s="13" t="s">
+      <c r="E36" s="12"/>
+    </row>
+    <row r="37" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B39" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E39" s="9"/>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B40" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C40" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D40" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="E40" s="15" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B38" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B39" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B40" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E41" s="3"/>
-    </row>
-    <row r="42" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="4" t="s">
+      <c r="E41" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B42" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="E42" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B43" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="C43" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B44" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3"/>
+    </row>
+    <row r="45" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>47</v>
+      <c r="D45" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/docs/doc.xlsx
+++ b/docs/doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_projects\BA-style-homepage-backend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75552B75-2B93-416F-9AA3-1F302A299C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68ABFC7B-01B3-48BD-9C3D-C1AE0220B805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
